--- a/fundos-para-analise.xlsx
+++ b/fundos-para-analise.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,22 +468,22 @@
         <v>ETF</v>
       </c>
       <c r="B3" t="str">
-        <v>QQQI11</v>
+        <v>DVID11</v>
       </c>
       <c r="C3" t="str">
         <v>etfs</v>
       </c>
       <c r="D3" t="str">
-        <v>https://statusinvest.com.br/etfs/qqqi11</v>
+        <v>https://statusinvest.com.br/etfs/dvid11</v>
       </c>
       <c r="E3" t="str">
-        <v>96,05</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>84,85</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>100,47</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v>Não</v>
@@ -500,22 +500,22 @@
         <v>ETF</v>
       </c>
       <c r="B4" t="str">
-        <v>SPYI11</v>
+        <v>QQQI11</v>
       </c>
       <c r="C4" t="str">
         <v>etfs</v>
       </c>
       <c r="D4" t="str">
-        <v>https://statusinvest.com.br/etfs/spyi11</v>
+        <v>https://statusinvest.com.br/etfs/qqqi11</v>
       </c>
       <c r="E4" t="str">
-        <v>108,70</v>
+        <v>96,05</v>
       </c>
       <c r="F4" t="str">
-        <v>97,33</v>
+        <v>84,85</v>
       </c>
       <c r="G4" t="str">
-        <v>111,57</v>
+        <v>100,47</v>
       </c>
       <c r="H4" t="str">
         <v>Não</v>
@@ -532,22 +532,22 @@
         <v>ETF</v>
       </c>
       <c r="B5" t="str">
-        <v>WRLD11</v>
+        <v>SPYI11</v>
       </c>
       <c r="C5" t="str">
         <v>etfs</v>
       </c>
       <c r="D5" t="str">
-        <v>https://statusinvest.com.br/etfs/wrld11</v>
+        <v>https://statusinvest.com.br/etfs/spyi11</v>
       </c>
       <c r="E5" t="str">
-        <v>148,36</v>
+        <v>108,70</v>
       </c>
       <c r="F5" t="str">
-        <v>127,35</v>
+        <v>97,33</v>
       </c>
       <c r="G5" t="str">
-        <v>148,84</v>
+        <v>111,57</v>
       </c>
       <c r="H5" t="str">
         <v>Não</v>
@@ -561,34 +561,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FIAGRO</v>
+        <v>ETF</v>
       </c>
       <c r="B6" t="str">
-        <v>FGAA11</v>
+        <v>WRLD11</v>
       </c>
       <c r="C6" t="str">
-        <v>fiagros</v>
+        <v>etfs</v>
       </c>
       <c r="D6" t="str">
-        <v>https://statusinvest.com.br/fiagros/fgaa11</v>
+        <v>https://statusinvest.com.br/etfs/wrld11</v>
       </c>
       <c r="E6" t="str">
-        <v>8,16</v>
+        <v>148,36</v>
       </c>
       <c r="F6" t="str">
-        <v>7,44</v>
+        <v>127,35</v>
       </c>
       <c r="G6" t="str">
-        <v>9,24</v>
+        <v>148,84</v>
       </c>
       <c r="H6" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I6" t="str">
-        <v>22/07/2026</v>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1262123&amp;cvm=true</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -596,31 +596,31 @@
         <v>FIAGRO</v>
       </c>
       <c r="B7" t="str">
-        <v>JGPX11</v>
+        <v>CPTR11</v>
       </c>
       <c r="C7" t="str">
         <v>fiagros</v>
       </c>
       <c r="D7" t="str">
-        <v>https://statusinvest.com.br/fiagros/jgpx11</v>
+        <v>https://statusinvest.com.br/fiagros/cptr11</v>
       </c>
       <c r="E7" t="str">
-        <v>60,20</v>
+        <v>8,10</v>
       </c>
       <c r="F7" t="str">
-        <v>57,76</v>
+        <v>6,51</v>
       </c>
       <c r="G7" t="str">
-        <v>70,86</v>
+        <v>8,46</v>
       </c>
       <c r="H7" t="str">
         <v>Sim</v>
       </c>
       <c r="I7" t="str">
-        <v>15/07/2026</v>
+        <v>02/08/2026</v>
       </c>
       <c r="J7" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1250216&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1273513&amp;cvm=true</v>
       </c>
     </row>
     <row r="8">
@@ -628,31 +628,31 @@
         <v>FIAGRO</v>
       </c>
       <c r="B8" t="str">
-        <v>KNCA11</v>
+        <v>FGAA11</v>
       </c>
       <c r="C8" t="str">
         <v>fiagros</v>
       </c>
       <c r="D8" t="str">
-        <v>https://statusinvest.com.br/fiagros/knca11</v>
+        <v>https://statusinvest.com.br/fiagros/fgaa11</v>
       </c>
       <c r="E8" t="str">
-        <v>89,50</v>
+        <v>8,16</v>
       </c>
       <c r="F8" t="str">
-        <v>82,87</v>
+        <v>7,44</v>
       </c>
       <c r="G8" t="str">
-        <v>95,93</v>
+        <v>9,24</v>
       </c>
       <c r="H8" t="str">
         <v>Sim</v>
       </c>
       <c r="I8" t="str">
-        <v>07/08/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="J8" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280657&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1262123&amp;cvm=true</v>
       </c>
     </row>
     <row r="9">
@@ -660,95 +660,95 @@
         <v>FIAGRO</v>
       </c>
       <c r="B9" t="str">
-        <v>RURA11</v>
+        <v>JGPX11</v>
       </c>
       <c r="C9" t="str">
         <v>fiagros</v>
       </c>
       <c r="D9" t="str">
-        <v>https://statusinvest.com.br/fiagros/rura11</v>
+        <v>https://statusinvest.com.br/fiagros/jgpx11</v>
       </c>
       <c r="E9" t="str">
-        <v>8,06</v>
+        <v>60,20</v>
       </c>
       <c r="F9" t="str">
-        <v>7,14</v>
+        <v>57,76</v>
       </c>
       <c r="G9" t="str">
-        <v>9,12</v>
+        <v>70,86</v>
       </c>
       <c r="H9" t="str">
         <v>Sim</v>
       </c>
       <c r="I9" t="str">
-        <v>10/07/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="J9" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1244447&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1250216&amp;cvm=true</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>INFRA</v>
+        <v>FIAGRO</v>
       </c>
       <c r="B10" t="str">
-        <v>BDIF11</v>
+        <v>KNCA11</v>
       </c>
       <c r="C10" t="str">
-        <v>fiinfras</v>
+        <v>fiagros</v>
       </c>
       <c r="D10" t="str">
-        <v>https://statusinvest.com.br/fiinfras/bdif11</v>
+        <v>https://statusinvest.com.br/fiagros/knca11</v>
       </c>
       <c r="E10" t="str">
-        <v>70,87</v>
+        <v>89,50</v>
       </c>
       <c r="F10" t="str">
-        <v>64,80</v>
+        <v>82,87</v>
       </c>
       <c r="G10" t="str">
-        <v>76,38</v>
+        <v>95,93</v>
       </c>
       <c r="H10" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>07/08/2026</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280657&amp;cvm=true</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>INFRA</v>
+        <v>FIAGRO</v>
       </c>
       <c r="B11" t="str">
-        <v>BIDB11</v>
+        <v>RURA11</v>
       </c>
       <c r="C11" t="str">
-        <v>fiinfras</v>
+        <v>fiagros</v>
       </c>
       <c r="D11" t="str">
-        <v>https://statusinvest.com.br/fiinfras/bidb11</v>
+        <v>https://statusinvest.com.br/fiagros/rura11</v>
       </c>
       <c r="E11" t="str">
-        <v>77,25</v>
+        <v>8,06</v>
       </c>
       <c r="F11" t="str">
-        <v>67,79</v>
+        <v>7,14</v>
       </c>
       <c r="G11" t="str">
-        <v>80,77</v>
+        <v>9,12</v>
       </c>
       <c r="H11" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>10/07/2026</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1244447&amp;cvm=true</v>
       </c>
     </row>
     <row r="12">
@@ -756,22 +756,22 @@
         <v>INFRA</v>
       </c>
       <c r="B12" t="str">
-        <v>CDII11</v>
+        <v>BDIF11</v>
       </c>
       <c r="C12" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D12" t="str">
-        <v>https://statusinvest.com.br/fiinfras/cdii11</v>
+        <v>https://statusinvest.com.br/fiinfras/bdif11</v>
       </c>
       <c r="E12" t="str">
-        <v>97,56</v>
+        <v>70,87</v>
       </c>
       <c r="F12" t="str">
-        <v>93,31</v>
+        <v>64,80</v>
       </c>
       <c r="G12" t="str">
-        <v>105,28</v>
+        <v>76,38</v>
       </c>
       <c r="H12" t="str">
         <v>Não</v>
@@ -788,22 +788,22 @@
         <v>INFRA</v>
       </c>
       <c r="B13" t="str">
-        <v>CPTI11</v>
+        <v>BIDB11</v>
       </c>
       <c r="C13" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D13" t="str">
-        <v>https://statusinvest.com.br/fiinfras/cpti11</v>
+        <v>https://statusinvest.com.br/fiinfras/bidb11</v>
       </c>
       <c r="E13" t="str">
-        <v>84,54</v>
+        <v>77,25</v>
       </c>
       <c r="F13" t="str">
-        <v>72,40</v>
+        <v>67,79</v>
       </c>
       <c r="G13" t="str">
-        <v>89,24</v>
+        <v>80,77</v>
       </c>
       <c r="H13" t="str">
         <v>Não</v>
@@ -820,22 +820,22 @@
         <v>INFRA</v>
       </c>
       <c r="B14" t="str">
-        <v>IFRA11</v>
+        <v>CDII11</v>
       </c>
       <c r="C14" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D14" t="str">
-        <v>https://statusinvest.com.br/fiinfras/ifra11</v>
+        <v>https://statusinvest.com.br/fiinfras/cdii11</v>
       </c>
       <c r="E14" t="str">
-        <v>91,47</v>
+        <v>97,56</v>
       </c>
       <c r="F14" t="str">
-        <v>84,83</v>
+        <v>93,31</v>
       </c>
       <c r="G14" t="str">
-        <v>101,09</v>
+        <v>105,28</v>
       </c>
       <c r="H14" t="str">
         <v>Não</v>
@@ -852,22 +852,22 @@
         <v>INFRA</v>
       </c>
       <c r="B15" t="str">
-        <v>JURO11</v>
+        <v>CPTI11</v>
       </c>
       <c r="C15" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D15" t="str">
-        <v>https://statusinvest.com.br/fiinfras/juro11</v>
+        <v>https://statusinvest.com.br/fiinfras/cpti11</v>
       </c>
       <c r="E15" t="str">
-        <v>95,44</v>
+        <v>84,54</v>
       </c>
       <c r="F15" t="str">
-        <v>88,58</v>
+        <v>72,40</v>
       </c>
       <c r="G15" t="str">
-        <v>104,30</v>
+        <v>89,24</v>
       </c>
       <c r="H15" t="str">
         <v>Não</v>
@@ -881,66 +881,66 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>PAPEL</v>
+        <v>INFRA</v>
       </c>
       <c r="B16" t="str">
-        <v>AFHI11</v>
+        <v>IFRA11</v>
       </c>
       <c r="C16" t="str">
-        <v>fundos-imobiliarios</v>
+        <v>fiinfras</v>
       </c>
       <c r="D16" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/afhi11</v>
+        <v>https://statusinvest.com.br/fiinfras/ifra11</v>
       </c>
       <c r="E16" t="str">
-        <v>94,50</v>
+        <v>91,47</v>
       </c>
       <c r="F16" t="str">
-        <v>82,12</v>
+        <v>84,83</v>
       </c>
       <c r="G16" t="str">
-        <v>96,43</v>
+        <v>101,09</v>
       </c>
       <c r="H16" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I16" t="str">
-        <v>23/07/2026</v>
+        <v/>
       </c>
       <c r="J16" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1263107&amp;cvm=true</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>PAPEL</v>
+        <v>INFRA</v>
       </c>
       <c r="B17" t="str">
-        <v>HGCR11</v>
+        <v>JURO11</v>
       </c>
       <c r="C17" t="str">
-        <v>fundos-imobiliarios</v>
+        <v>fiinfras</v>
       </c>
       <c r="D17" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/hgcr11</v>
+        <v>https://statusinvest.com.br/fiinfras/juro11</v>
       </c>
       <c r="E17" t="str">
-        <v>91,53</v>
+        <v>95,44</v>
       </c>
       <c r="F17" t="str">
-        <v>83,56</v>
+        <v>88,58</v>
       </c>
       <c r="G17" t="str">
-        <v>99,48</v>
+        <v>104,30</v>
       </c>
       <c r="H17" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I17" t="str">
-        <v>13/07/2026</v>
+        <v/>
       </c>
       <c r="J17" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246185&amp;cvm=true</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -948,31 +948,31 @@
         <v>PAPEL</v>
       </c>
       <c r="B18" t="str">
-        <v>KNCR11</v>
+        <v>AFHI11</v>
       </c>
       <c r="C18" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D18" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/kncr11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/afhi11</v>
       </c>
       <c r="E18" t="str">
-        <v>106,64</v>
+        <v>94,50</v>
       </c>
       <c r="F18" t="str">
-        <v>92,11</v>
+        <v>82,12</v>
       </c>
       <c r="G18" t="str">
-        <v>108,56</v>
+        <v>96,43</v>
       </c>
       <c r="H18" t="str">
         <v>Sim</v>
       </c>
       <c r="I18" t="str">
-        <v>08/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="J18" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1242367&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1263107&amp;cvm=true</v>
       </c>
     </row>
     <row r="19">
@@ -980,31 +980,31 @@
         <v>PAPEL</v>
       </c>
       <c r="B19" t="str">
-        <v>KNIP11</v>
+        <v>HGCR11</v>
       </c>
       <c r="C19" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D19" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/knip11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/hgcr11</v>
       </c>
       <c r="E19" t="str">
-        <v>90,37</v>
+        <v>91,53</v>
       </c>
       <c r="F19" t="str">
-        <v>79,81</v>
+        <v>83,56</v>
       </c>
       <c r="G19" t="str">
-        <v>94,00</v>
+        <v>99,48</v>
       </c>
       <c r="H19" t="str">
         <v>Sim</v>
       </c>
       <c r="I19" t="str">
-        <v>08/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="J19" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1242372&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246185&amp;cvm=true</v>
       </c>
     </row>
     <row r="20">
@@ -1012,31 +1012,31 @@
         <v>PAPEL</v>
       </c>
       <c r="B20" t="str">
-        <v>KNRI11</v>
+        <v>KNCR11</v>
       </c>
       <c r="C20" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D20" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/knri11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/kncr11</v>
       </c>
       <c r="E20" t="str">
-        <v>154,11</v>
+        <v>106,64</v>
       </c>
       <c r="F20" t="str">
-        <v>129,08</v>
+        <v>92,11</v>
       </c>
       <c r="G20" t="str">
-        <v>169,98</v>
+        <v>108,56</v>
       </c>
       <c r="H20" t="str">
         <v>Sim</v>
       </c>
       <c r="I20" t="str">
-        <v>04/08/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="J20" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1276289&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1242367&amp;cvm=true</v>
       </c>
     </row>
     <row r="21">
@@ -1044,31 +1044,31 @@
         <v>PAPEL</v>
       </c>
       <c r="B21" t="str">
-        <v>KNSC11</v>
+        <v>KNIP11</v>
       </c>
       <c r="C21" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D21" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/knsc11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/knip11</v>
       </c>
       <c r="E21" t="str">
-        <v>9,00</v>
+        <v>90,37</v>
       </c>
       <c r="F21" t="str">
-        <v>7,70</v>
+        <v>79,81</v>
       </c>
       <c r="G21" t="str">
-        <v>9,23</v>
+        <v>94,00</v>
       </c>
       <c r="H21" t="str">
         <v>Sim</v>
       </c>
       <c r="I21" t="str">
-        <v>31/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="J21" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1272069&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1242372&amp;cvm=true</v>
       </c>
     </row>
     <row r="22">
@@ -1076,95 +1076,95 @@
         <v>PAPEL</v>
       </c>
       <c r="B22" t="str">
-        <v>PCIP11</v>
+        <v>KNRI11</v>
       </c>
       <c r="C22" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D22" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/pcip11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/knri11</v>
       </c>
       <c r="E22" t="str">
-        <v>75,20</v>
+        <v>154,11</v>
       </c>
       <c r="F22" t="str">
-        <v>72,92</v>
+        <v>129,08</v>
       </c>
       <c r="G22" t="str">
-        <v>85,71</v>
+        <v>169,98</v>
       </c>
       <c r="H22" t="str">
         <v>Sim</v>
       </c>
       <c r="I22" t="str">
-        <v>21/07/2026</v>
+        <v>04/08/2026</v>
       </c>
       <c r="J22" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1261593&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1276289&amp;cvm=true</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>TIJOLO</v>
+        <v>PAPEL</v>
       </c>
       <c r="B23" t="str">
-        <v>ALZR11</v>
+        <v>KNSC11</v>
       </c>
       <c r="C23" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D23" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/alzr11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/knsc11</v>
       </c>
       <c r="E23" t="str">
-        <v>9,92</v>
+        <v>9,00</v>
       </c>
       <c r="F23" t="str">
-        <v>9,32</v>
+        <v>7,70</v>
       </c>
       <c r="G23" t="str">
-        <v>10,62</v>
+        <v>9,23</v>
       </c>
       <c r="H23" t="str">
         <v>Sim</v>
       </c>
       <c r="I23" t="str">
-        <v>20/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="J23" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1260198&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1272069&amp;cvm=true</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TIJOLO</v>
+        <v>PAPEL</v>
       </c>
       <c r="B24" t="str">
-        <v>BTLG11</v>
+        <v>PCIP11</v>
       </c>
       <c r="C24" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D24" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/btlg11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/pcip11</v>
       </c>
       <c r="E24" t="str">
-        <v>100,73</v>
+        <v>75,20</v>
       </c>
       <c r="F24" t="str">
-        <v>91,41</v>
+        <v>72,92</v>
       </c>
       <c r="G24" t="str">
-        <v>103,92</v>
+        <v>85,71</v>
       </c>
       <c r="H24" t="str">
         <v>Sim</v>
       </c>
       <c r="I24" t="str">
-        <v>05/08/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="J24" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1277934&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1261593&amp;cvm=true</v>
       </c>
     </row>
     <row r="25">
@@ -1172,31 +1172,31 @@
         <v>TIJOLO</v>
       </c>
       <c r="B25" t="str">
-        <v>HGLG11</v>
+        <v>ALZR11</v>
       </c>
       <c r="C25" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D25" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/hglg11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/alzr11</v>
       </c>
       <c r="E25" t="str">
-        <v>147,00</v>
+        <v>9,92</v>
       </c>
       <c r="F25" t="str">
-        <v>141,81</v>
+        <v>9,32</v>
       </c>
       <c r="G25" t="str">
-        <v>156,90</v>
+        <v>10,62</v>
       </c>
       <c r="H25" t="str">
         <v>Sim</v>
       </c>
       <c r="I25" t="str">
-        <v>13/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="J25" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246174&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1260198&amp;cvm=true</v>
       </c>
     </row>
     <row r="26">
@@ -1204,31 +1204,31 @@
         <v>TIJOLO</v>
       </c>
       <c r="B26" t="str">
-        <v>HGRU11</v>
+        <v>BTLG11</v>
       </c>
       <c r="C26" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D26" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/hgru11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/btlg11</v>
       </c>
       <c r="E26" t="str">
-        <v>119,25</v>
+        <v>100,73</v>
       </c>
       <c r="F26" t="str">
-        <v>112,62</v>
+        <v>91,41</v>
       </c>
       <c r="G26" t="str">
-        <v>132,90</v>
+        <v>103,92</v>
       </c>
       <c r="H26" t="str">
         <v>Sim</v>
       </c>
       <c r="I26" t="str">
-        <v>13/07/2026</v>
+        <v>05/08/2026</v>
       </c>
       <c r="J26" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246173&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1277934&amp;cvm=true</v>
       </c>
     </row>
     <row r="27">
@@ -1236,31 +1236,31 @@
         <v>TIJOLO</v>
       </c>
       <c r="B27" t="str">
-        <v>HSML11</v>
+        <v>HGLG11</v>
       </c>
       <c r="C27" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D27" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/hsml11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/hglg11</v>
       </c>
       <c r="E27" t="str">
-        <v>83,53</v>
+        <v>147,00</v>
       </c>
       <c r="F27" t="str">
-        <v>73,96</v>
+        <v>141,81</v>
       </c>
       <c r="G27" t="str">
-        <v>95,19</v>
+        <v>156,90</v>
       </c>
       <c r="H27" t="str">
         <v>Sim</v>
       </c>
       <c r="I27" t="str">
-        <v>07/08/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="J27" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280449&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246174&amp;cvm=true</v>
       </c>
     </row>
     <row r="28">
@@ -1268,31 +1268,31 @@
         <v>TIJOLO</v>
       </c>
       <c r="B28" t="str">
-        <v>TRXF11</v>
+        <v>HGRU11</v>
       </c>
       <c r="C28" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D28" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/trxf11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/hgru11</v>
       </c>
       <c r="E28" t="str">
-        <v>85,90</v>
+        <v>119,25</v>
       </c>
       <c r="F28" t="str">
-        <v>84,41</v>
+        <v>112,62</v>
       </c>
       <c r="G28" t="str">
-        <v>95,41</v>
+        <v>132,90</v>
       </c>
       <c r="H28" t="str">
         <v>Sim</v>
       </c>
       <c r="I28" t="str">
-        <v>06/08/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="J28" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1278135&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246173&amp;cvm=true</v>
       </c>
     </row>
     <row r="29">
@@ -1300,22 +1300,22 @@
         <v>TIJOLO</v>
       </c>
       <c r="B29" t="str">
-        <v>XPML11</v>
+        <v>HSML11</v>
       </c>
       <c r="C29" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D29" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/xpml11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/hsml11</v>
       </c>
       <c r="E29" t="str">
-        <v>104,55</v>
+        <v>83,53</v>
       </c>
       <c r="F29" t="str">
-        <v>92,00</v>
+        <v>73,96</v>
       </c>
       <c r="G29" t="str">
-        <v>111,25</v>
+        <v>95,19</v>
       </c>
       <c r="H29" t="str">
         <v>Sim</v>
@@ -1324,71 +1324,71 @@
         <v>07/08/2026</v>
       </c>
       <c r="J29" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280401&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280449&amp;cvm=true</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>VENDA</v>
+        <v>TIJOLO</v>
       </c>
       <c r="B30" t="str">
-        <v>ALUG11</v>
+        <v>TRXF11</v>
       </c>
       <c r="C30" t="str">
-        <v>etfs</v>
+        <v>fundos-imobiliarios</v>
       </c>
       <c r="D30" t="str">
-        <v>https://statusinvest.com.br/etfs/alug11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/trxf11</v>
       </c>
       <c r="E30" t="str">
-        <v>42,76</v>
+        <v>85,90</v>
       </c>
       <c r="F30" t="str">
-        <v>38,80</v>
+        <v>84,41</v>
       </c>
       <c r="G30" t="str">
-        <v>44,18</v>
+        <v>95,41</v>
       </c>
       <c r="H30" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>06/08/2026</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1278135&amp;cvm=true</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>VENDA</v>
+        <v>TIJOLO</v>
       </c>
       <c r="B31" t="str">
-        <v>BODB11</v>
+        <v>XPML11</v>
       </c>
       <c r="C31" t="str">
-        <v>fiinfras</v>
+        <v>fundos-imobiliarios</v>
       </c>
       <c r="D31" t="str">
-        <v>https://statusinvest.com.br/fiinfras/bodb11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/xpml11</v>
       </c>
       <c r="E31" t="str">
-        <v>7,26</v>
+        <v>104,55</v>
       </c>
       <c r="F31" t="str">
-        <v>6,31</v>
+        <v>92,00</v>
       </c>
       <c r="G31" t="str">
-        <v>7,98</v>
+        <v>111,25</v>
       </c>
       <c r="H31" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>07/08/2026</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280401&amp;cvm=true</v>
       </c>
     </row>
     <row r="32">
@@ -1396,31 +1396,31 @@
         <v>VENDA</v>
       </c>
       <c r="B32" t="str">
-        <v>BRCR11</v>
+        <v>ALUG11</v>
       </c>
       <c r="C32" t="str">
-        <v>fundos-imobiliarios</v>
+        <v>etfs</v>
       </c>
       <c r="D32" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/brcr11</v>
+        <v>https://statusinvest.com.br/etfs/alug11</v>
       </c>
       <c r="E32" t="str">
-        <v>39,61</v>
+        <v>42,76</v>
       </c>
       <c r="F32" t="str">
-        <v>37,04</v>
+        <v>38,80</v>
       </c>
       <c r="G32" t="str">
-        <v>48,96</v>
+        <v>44,18</v>
       </c>
       <c r="H32" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I32" t="str">
-        <v>05/08/2026</v>
+        <v/>
       </c>
       <c r="J32" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1277921&amp;cvm=true</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1428,31 +1428,31 @@
         <v>VENDA</v>
       </c>
       <c r="B33" t="str">
-        <v>BTRA11</v>
+        <v>BODB11</v>
       </c>
       <c r="C33" t="str">
-        <v>fundos-imobiliarios</v>
+        <v>fiinfras</v>
       </c>
       <c r="D33" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/btra11</v>
+        <v>https://statusinvest.com.br/fiinfras/bodb11</v>
       </c>
       <c r="E33" t="str">
-        <v>64,05</v>
+        <v>7,26</v>
       </c>
       <c r="F33" t="str">
-        <v>45,51</v>
+        <v>6,31</v>
       </c>
       <c r="G33" t="str">
-        <v>67,81</v>
+        <v>7,98</v>
       </c>
       <c r="H33" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I33" t="str">
-        <v>23/01/2026</v>
+        <v/>
       </c>
       <c r="J33" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1091462&amp;cvm=true</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1460,31 +1460,31 @@
         <v>VENDA</v>
       </c>
       <c r="B34" t="str">
-        <v>FYTO11</v>
+        <v>BRCR11</v>
       </c>
       <c r="C34" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D34" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/fyto11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/brcr11</v>
       </c>
       <c r="E34" t="str">
-        <v>8,01</v>
+        <v>39,61</v>
       </c>
       <c r="F34" t="str">
-        <v>7,02</v>
+        <v>37,04</v>
       </c>
       <c r="G34" t="str">
-        <v>8,64</v>
+        <v>48,96</v>
       </c>
       <c r="H34" t="str">
         <v>Sim</v>
       </c>
       <c r="I34" t="str">
-        <v>07/08/2026</v>
+        <v>05/08/2026</v>
       </c>
       <c r="J34" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280453&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1277921&amp;cvm=true</v>
       </c>
     </row>
     <row r="35">
@@ -1492,31 +1492,31 @@
         <v>VENDA</v>
       </c>
       <c r="B35" t="str">
-        <v>GCRA11</v>
+        <v>BTRA11</v>
       </c>
       <c r="C35" t="str">
-        <v>fiagros</v>
+        <v>fundos-imobiliarios</v>
       </c>
       <c r="D35" t="str">
-        <v>https://statusinvest.com.br/fiagros/gcra11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/btra11</v>
       </c>
       <c r="E35" t="str">
-        <v>49,98</v>
+        <v>64,05</v>
       </c>
       <c r="F35" t="str">
-        <v>44,84</v>
+        <v>45,51</v>
       </c>
       <c r="G35" t="str">
-        <v>55,56</v>
+        <v>67,81</v>
       </c>
       <c r="H35" t="str">
         <v>Sim</v>
       </c>
       <c r="I35" t="str">
-        <v>31/07/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="J35" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1272504&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1091462&amp;cvm=true</v>
       </c>
     </row>
     <row r="36">
@@ -1524,31 +1524,31 @@
         <v>VENDA</v>
       </c>
       <c r="B36" t="str">
-        <v>GCRI11</v>
+        <v>FYTO11</v>
       </c>
       <c r="C36" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D36" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/gcri11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/fyto11</v>
       </c>
       <c r="E36" t="str">
-        <v>65,20</v>
+        <v>8,01</v>
       </c>
       <c r="F36" t="str">
-        <v>55,81</v>
+        <v>7,02</v>
       </c>
       <c r="G36" t="str">
-        <v>70,31</v>
+        <v>8,64</v>
       </c>
       <c r="H36" t="str">
         <v>Sim</v>
       </c>
       <c r="I36" t="str">
-        <v>30/07/2026</v>
+        <v>07/08/2026</v>
       </c>
       <c r="J36" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1271046&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280453&amp;cvm=true</v>
       </c>
     </row>
     <row r="37">
@@ -1556,31 +1556,31 @@
         <v>VENDA</v>
       </c>
       <c r="B37" t="str">
-        <v>HGRE11</v>
+        <v>GCRA11</v>
       </c>
       <c r="C37" t="str">
-        <v>fundos-imobiliarios</v>
+        <v>fiagros</v>
       </c>
       <c r="D37" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/hgre11</v>
+        <v>https://statusinvest.com.br/fiagros/gcra11</v>
       </c>
       <c r="E37" t="str">
-        <v>117,30</v>
+        <v>49,98</v>
       </c>
       <c r="F37" t="str">
-        <v>100,53</v>
+        <v>44,84</v>
       </c>
       <c r="G37" t="str">
-        <v>131,55</v>
+        <v>55,56</v>
       </c>
       <c r="H37" t="str">
         <v>Sim</v>
       </c>
       <c r="I37" t="str">
-        <v>13/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="J37" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246183&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1272504&amp;cvm=true</v>
       </c>
     </row>
     <row r="38">
@@ -1588,31 +1588,31 @@
         <v>VENDA</v>
       </c>
       <c r="B38" t="str">
-        <v>IBCR11</v>
+        <v>GCRI11</v>
       </c>
       <c r="C38" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D38" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/ibcr11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/gcri11</v>
       </c>
       <c r="E38" t="str">
-        <v>40,53</v>
+        <v>65,20</v>
       </c>
       <c r="F38" t="str">
-        <v>39,89</v>
+        <v>55,81</v>
       </c>
       <c r="G38" t="str">
-        <v>55,64</v>
+        <v>70,31</v>
       </c>
       <c r="H38" t="str">
         <v>Sim</v>
       </c>
       <c r="I38" t="str">
-        <v>01/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="J38" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1237809&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1271046&amp;cvm=true</v>
       </c>
     </row>
     <row r="39">
@@ -1620,22 +1620,22 @@
         <v>VENDA</v>
       </c>
       <c r="B39" t="str">
-        <v>RBRL11</v>
+        <v>HGRE11</v>
       </c>
       <c r="C39" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D39" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/rbrl11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/hgre11</v>
       </c>
       <c r="E39" t="str">
-        <v>71,80</v>
+        <v>117,30</v>
       </c>
       <c r="F39" t="str">
-        <v>71,10</v>
+        <v>100,53</v>
       </c>
       <c r="G39" t="str">
-        <v>91,83</v>
+        <v>131,55</v>
       </c>
       <c r="H39" t="str">
         <v>Sim</v>
@@ -1644,7 +1644,7 @@
         <v>13/07/2026</v>
       </c>
       <c r="J39" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246171&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246183&amp;cvm=true</v>
       </c>
     </row>
     <row r="40">
@@ -1652,31 +1652,31 @@
         <v>VENDA</v>
       </c>
       <c r="B40" t="str">
-        <v>RBRP11</v>
+        <v>IBCR11</v>
       </c>
       <c r="C40" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D40" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/rbrp11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/ibcr11</v>
       </c>
       <c r="E40" t="str">
-        <v>42,67</v>
+        <v>40,53</v>
       </c>
       <c r="F40" t="str">
-        <v>42,39</v>
+        <v>39,89</v>
       </c>
       <c r="G40" t="str">
-        <v>54,15</v>
+        <v>55,64</v>
       </c>
       <c r="H40" t="str">
         <v>Sim</v>
       </c>
       <c r="I40" t="str">
-        <v>21/07/2026</v>
+        <v>01/07/2026</v>
       </c>
       <c r="J40" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1261592&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1237809&amp;cvm=true</v>
       </c>
     </row>
     <row r="41">
@@ -1684,31 +1684,31 @@
         <v>VENDA</v>
       </c>
       <c r="B41" t="str">
-        <v>RBRR11</v>
+        <v>RBRL11</v>
       </c>
       <c r="C41" t="str">
         <v>fundos-imobiliarios</v>
       </c>
       <c r="D41" t="str">
-        <v>https://statusinvest.com.br/fundos-imobiliarios/rbrr11</v>
+        <v>https://statusinvest.com.br/fundos-imobiliarios/rbrl11</v>
       </c>
       <c r="E41" t="str">
-        <v>76,33</v>
+        <v>71,80</v>
       </c>
       <c r="F41" t="str">
-        <v>75,07</v>
+        <v>71,10</v>
       </c>
       <c r="G41" t="str">
-        <v>87,83</v>
+        <v>91,83</v>
       </c>
       <c r="H41" t="str">
         <v>Sim</v>
       </c>
       <c r="I41" t="str">
-        <v>21/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="J41" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1261615&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1246171&amp;cvm=true</v>
       </c>
     </row>
     <row r="42">
@@ -1716,36 +1716,100 @@
         <v>VENDA</v>
       </c>
       <c r="B42" t="str">
+        <v>RBRP11</v>
+      </c>
+      <c r="C42" t="str">
+        <v>fundos-imobiliarios</v>
+      </c>
+      <c r="D42" t="str">
+        <v>https://statusinvest.com.br/fundos-imobiliarios/rbrp11</v>
+      </c>
+      <c r="E42" t="str">
+        <v>42,67</v>
+      </c>
+      <c r="F42" t="str">
+        <v>42,39</v>
+      </c>
+      <c r="G42" t="str">
+        <v>54,15</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="I42" t="str">
+        <v>21/07/2026</v>
+      </c>
+      <c r="J42" t="str">
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1261592&amp;cvm=true</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>VENDA</v>
+      </c>
+      <c r="B43" t="str">
+        <v>RBRR11</v>
+      </c>
+      <c r="C43" t="str">
+        <v>fundos-imobiliarios</v>
+      </c>
+      <c r="D43" t="str">
+        <v>https://statusinvest.com.br/fundos-imobiliarios/rbrr11</v>
+      </c>
+      <c r="E43" t="str">
+        <v>76,33</v>
+      </c>
+      <c r="F43" t="str">
+        <v>75,07</v>
+      </c>
+      <c r="G43" t="str">
+        <v>87,83</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="I43" t="str">
+        <v>21/07/2026</v>
+      </c>
+      <c r="J43" t="str">
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1261615&amp;cvm=true</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>VENDA</v>
+      </c>
+      <c r="B44" t="str">
         <v>URPR11</v>
       </c>
-      <c r="C42" t="str">
-        <v>fundos-imobiliarios</v>
-      </c>
-      <c r="D42" t="str">
+      <c r="C44" t="str">
+        <v>fundos-imobiliarios</v>
+      </c>
+      <c r="D44" t="str">
         <v>https://statusinvest.com.br/fundos-imobiliarios/urpr11</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E44" t="str">
         <v>18,29</v>
       </c>
-      <c r="F42" t="str">
+      <c r="F44" t="str">
         <v>18,29</v>
       </c>
-      <c r="G42" t="str">
+      <c r="G44" t="str">
         <v>41,77</v>
       </c>
-      <c r="H42" t="str">
-        <v>Sim</v>
-      </c>
-      <c r="I42" t="str">
+      <c r="H44" t="str">
+        <v>Sim</v>
+      </c>
+      <c r="I44" t="str">
         <v>31/07/2026</v>
       </c>
-      <c r="J42" t="str">
+      <c r="J44" t="str">
         <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1271949&amp;cvm=true</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/fundos-para-analise.xlsx
+++ b/fundos-para-analise.xlsx
@@ -468,22 +468,22 @@
         <v>ETF</v>
       </c>
       <c r="B3" t="str">
-        <v>DVID11</v>
+        <v>QQQI11</v>
       </c>
       <c r="C3" t="str">
         <v>etfs</v>
       </c>
       <c r="D3" t="str">
-        <v>https://statusinvest.com.br/etfs/dvid11</v>
+        <v>https://statusinvest.com.br/etfs/qqqi11</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>96,05</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>84,85</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>100,47</v>
       </c>
       <c r="H3" t="str">
         <v>Não</v>
@@ -500,22 +500,22 @@
         <v>ETF</v>
       </c>
       <c r="B4" t="str">
-        <v>QQQI11</v>
+        <v>SPYI11</v>
       </c>
       <c r="C4" t="str">
         <v>etfs</v>
       </c>
       <c r="D4" t="str">
-        <v>https://statusinvest.com.br/etfs/qqqi11</v>
+        <v>https://statusinvest.com.br/etfs/spyi11</v>
       </c>
       <c r="E4" t="str">
-        <v>96,05</v>
+        <v>108,70</v>
       </c>
       <c r="F4" t="str">
-        <v>84,85</v>
+        <v>97,33</v>
       </c>
       <c r="G4" t="str">
-        <v>100,47</v>
+        <v>111,57</v>
       </c>
       <c r="H4" t="str">
         <v>Não</v>
@@ -532,22 +532,22 @@
         <v>ETF</v>
       </c>
       <c r="B5" t="str">
-        <v>SPYI11</v>
+        <v>WRLD11</v>
       </c>
       <c r="C5" t="str">
         <v>etfs</v>
       </c>
       <c r="D5" t="str">
-        <v>https://statusinvest.com.br/etfs/spyi11</v>
+        <v>https://statusinvest.com.br/etfs/wrld11</v>
       </c>
       <c r="E5" t="str">
-        <v>108,70</v>
+        <v>148,36</v>
       </c>
       <c r="F5" t="str">
-        <v>97,33</v>
+        <v>127,35</v>
       </c>
       <c r="G5" t="str">
-        <v>111,57</v>
+        <v>148,84</v>
       </c>
       <c r="H5" t="str">
         <v>Não</v>
@@ -561,34 +561,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ETF</v>
+        <v>FIAGRO</v>
       </c>
       <c r="B6" t="str">
-        <v>WRLD11</v>
+        <v>CPTR11</v>
       </c>
       <c r="C6" t="str">
-        <v>etfs</v>
+        <v>fiagros</v>
       </c>
       <c r="D6" t="str">
-        <v>https://statusinvest.com.br/etfs/wrld11</v>
+        <v>https://statusinvest.com.br/fiagros/cptr11</v>
       </c>
       <c r="E6" t="str">
-        <v>148,36</v>
+        <v>8,10</v>
       </c>
       <c r="F6" t="str">
-        <v>127,35</v>
+        <v>6,51</v>
       </c>
       <c r="G6" t="str">
-        <v>148,84</v>
+        <v>8,46</v>
       </c>
       <c r="H6" t="str">
-        <v>Não</v>
+        <v>Sim</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>02/08/2026</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1273513&amp;cvm=true</v>
       </c>
     </row>
     <row r="7">
@@ -596,31 +596,31 @@
         <v>FIAGRO</v>
       </c>
       <c r="B7" t="str">
-        <v>CPTR11</v>
+        <v>FGAA11</v>
       </c>
       <c r="C7" t="str">
         <v>fiagros</v>
       </c>
       <c r="D7" t="str">
-        <v>https://statusinvest.com.br/fiagros/cptr11</v>
+        <v>https://statusinvest.com.br/fiagros/fgaa11</v>
       </c>
       <c r="E7" t="str">
-        <v>8,10</v>
+        <v>8,16</v>
       </c>
       <c r="F7" t="str">
-        <v>6,51</v>
+        <v>7,44</v>
       </c>
       <c r="G7" t="str">
-        <v>8,46</v>
+        <v>9,24</v>
       </c>
       <c r="H7" t="str">
         <v>Sim</v>
       </c>
       <c r="I7" t="str">
-        <v>02/08/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="J7" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1273513&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1262123&amp;cvm=true</v>
       </c>
     </row>
     <row r="8">
@@ -628,31 +628,31 @@
         <v>FIAGRO</v>
       </c>
       <c r="B8" t="str">
-        <v>FGAA11</v>
+        <v>JGPX11</v>
       </c>
       <c r="C8" t="str">
         <v>fiagros</v>
       </c>
       <c r="D8" t="str">
-        <v>https://statusinvest.com.br/fiagros/fgaa11</v>
+        <v>https://statusinvest.com.br/fiagros/jgpx11</v>
       </c>
       <c r="E8" t="str">
-        <v>8,16</v>
+        <v>60,20</v>
       </c>
       <c r="F8" t="str">
-        <v>7,44</v>
+        <v>57,76</v>
       </c>
       <c r="G8" t="str">
-        <v>9,24</v>
+        <v>70,86</v>
       </c>
       <c r="H8" t="str">
         <v>Sim</v>
       </c>
       <c r="I8" t="str">
-        <v>22/07/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="J8" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1262123&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1250216&amp;cvm=true</v>
       </c>
     </row>
     <row r="9">
@@ -660,31 +660,31 @@
         <v>FIAGRO</v>
       </c>
       <c r="B9" t="str">
-        <v>JGPX11</v>
+        <v>KNCA11</v>
       </c>
       <c r="C9" t="str">
         <v>fiagros</v>
       </c>
       <c r="D9" t="str">
-        <v>https://statusinvest.com.br/fiagros/jgpx11</v>
+        <v>https://statusinvest.com.br/fiagros/knca11</v>
       </c>
       <c r="E9" t="str">
-        <v>60,20</v>
+        <v>89,50</v>
       </c>
       <c r="F9" t="str">
-        <v>57,76</v>
+        <v>82,87</v>
       </c>
       <c r="G9" t="str">
-        <v>70,86</v>
+        <v>95,93</v>
       </c>
       <c r="H9" t="str">
         <v>Sim</v>
       </c>
       <c r="I9" t="str">
-        <v>15/07/2026</v>
+        <v>07/08/2026</v>
       </c>
       <c r="J9" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1250216&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280657&amp;cvm=true</v>
       </c>
     </row>
     <row r="10">
@@ -692,63 +692,63 @@
         <v>FIAGRO</v>
       </c>
       <c r="B10" t="str">
-        <v>KNCA11</v>
+        <v>RURA11</v>
       </c>
       <c r="C10" t="str">
         <v>fiagros</v>
       </c>
       <c r="D10" t="str">
-        <v>https://statusinvest.com.br/fiagros/knca11</v>
+        <v>https://statusinvest.com.br/fiagros/rura11</v>
       </c>
       <c r="E10" t="str">
-        <v>89,50</v>
+        <v>8,06</v>
       </c>
       <c r="F10" t="str">
-        <v>82,87</v>
+        <v>7,14</v>
       </c>
       <c r="G10" t="str">
-        <v>95,93</v>
+        <v>9,12</v>
       </c>
       <c r="H10" t="str">
         <v>Sim</v>
       </c>
       <c r="I10" t="str">
-        <v>07/08/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="J10" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1280657&amp;cvm=true</v>
+        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1244447&amp;cvm=true</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>FIAGRO</v>
+        <v>INFRA</v>
       </c>
       <c r="B11" t="str">
-        <v>RURA11</v>
+        <v>BDIF11</v>
       </c>
       <c r="C11" t="str">
-        <v>fiagros</v>
+        <v>fiinfras</v>
       </c>
       <c r="D11" t="str">
-        <v>https://statusinvest.com.br/fiagros/rura11</v>
+        <v>https://statusinvest.com.br/fiinfras/bdif11</v>
       </c>
       <c r="E11" t="str">
-        <v>8,06</v>
+        <v>70,87</v>
       </c>
       <c r="F11" t="str">
-        <v>7,14</v>
+        <v>64,80</v>
       </c>
       <c r="G11" t="str">
-        <v>9,12</v>
+        <v>76,38</v>
       </c>
       <c r="H11" t="str">
-        <v>Sim</v>
+        <v>Não</v>
       </c>
       <c r="I11" t="str">
-        <v>10/07/2026</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>https://fnet.bmfbovespa.com.br/fnet/publico/exibirDocumento?id=1244447&amp;cvm=true</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -756,22 +756,22 @@
         <v>INFRA</v>
       </c>
       <c r="B12" t="str">
-        <v>BDIF11</v>
+        <v>BIDB11</v>
       </c>
       <c r="C12" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D12" t="str">
-        <v>https://statusinvest.com.br/fiinfras/bdif11</v>
+        <v>https://statusinvest.com.br/fiinfras/bidb11</v>
       </c>
       <c r="E12" t="str">
-        <v>70,87</v>
+        <v>77,25</v>
       </c>
       <c r="F12" t="str">
-        <v>64,80</v>
+        <v>67,79</v>
       </c>
       <c r="G12" t="str">
-        <v>76,38</v>
+        <v>80,77</v>
       </c>
       <c r="H12" t="str">
         <v>Não</v>
@@ -788,22 +788,22 @@
         <v>INFRA</v>
       </c>
       <c r="B13" t="str">
-        <v>BIDB11</v>
+        <v>CDII11</v>
       </c>
       <c r="C13" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D13" t="str">
-        <v>https://statusinvest.com.br/fiinfras/bidb11</v>
+        <v>https://statusinvest.com.br/fiinfras/cdii11</v>
       </c>
       <c r="E13" t="str">
-        <v>77,25</v>
+        <v>97,56</v>
       </c>
       <c r="F13" t="str">
-        <v>67,79</v>
+        <v>93,31</v>
       </c>
       <c r="G13" t="str">
-        <v>80,77</v>
+        <v>105,28</v>
       </c>
       <c r="H13" t="str">
         <v>Não</v>
@@ -820,22 +820,22 @@
         <v>INFRA</v>
       </c>
       <c r="B14" t="str">
-        <v>CDII11</v>
+        <v>CPTI11</v>
       </c>
       <c r="C14" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D14" t="str">
-        <v>https://statusinvest.com.br/fiinfras/cdii11</v>
+        <v>https://statusinvest.com.br/fiinfras/cpti11</v>
       </c>
       <c r="E14" t="str">
-        <v>97,56</v>
+        <v>84,54</v>
       </c>
       <c r="F14" t="str">
-        <v>93,31</v>
+        <v>72,40</v>
       </c>
       <c r="G14" t="str">
-        <v>105,28</v>
+        <v>89,24</v>
       </c>
       <c r="H14" t="str">
         <v>Não</v>
@@ -852,22 +852,22 @@
         <v>INFRA</v>
       </c>
       <c r="B15" t="str">
-        <v>CPTI11</v>
+        <v>DIVD11</v>
       </c>
       <c r="C15" t="str">
         <v>fiinfras</v>
       </c>
       <c r="D15" t="str">
-        <v>https://statusinvest.com.br/fiinfras/cpti11</v>
+        <v>https://statusinvest.com.br/fiinfras/divd11</v>
       </c>
       <c r="E15" t="str">
-        <v>84,54</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>72,40</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>89,24</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>Não</v>
